--- a/12620764.xlsx
+++ b/12620764.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mishty sharma\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F1A4539-B367-4264-82F9-0B1601F4EE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98FAD21-1B71-43BE-8892-763C0DDE46C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,15 @@
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -1038,7 +1047,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
+      <c r="A7" s="8">
         <v>46252</v>
       </c>
       <c r="B7" s="14">
@@ -1063,11 +1072,11 @@
         <v>20</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <f t="shared" ref="I7:I69" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>850</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" ref="J6:J69" si="1">IF(I7="","",1440-I7)</f>
+        <f t="shared" ref="J7:J69" si="1">IF(I7="","",1440-I7)</f>
         <v>590</v>
       </c>
       <c r="K7" s="16" t="s">
@@ -1084,7 +1093,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13">
+      <c r="A8" s="8">
         <v>46253</v>
       </c>
       <c r="B8" s="14">

--- a/12620764.xlsx
+++ b/12620764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mishty sharma\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98FAD21-1B71-43BE-8892-763C0DDE46C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B79F4F-68D9-4D29-9B12-5FB06BED2957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,21 @@
   </si>
   <si>
     <t>AUGUST</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>feeling good today</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>neutral</t>
   </si>
 </sst>
 </file>
@@ -1139,48 +1154,96 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B9" s="14">
+        <v>360</v>
+      </c>
+      <c r="C9" s="14">
+        <v>20</v>
+      </c>
+      <c r="D9" s="14">
+        <v>100</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>400</v>
+      </c>
+      <c r="G9" s="14">
+        <v>8</v>
+      </c>
+      <c r="H9" s="14">
+        <v>20</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="14">
+        <v>400</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>100</v>
+      </c>
+      <c r="E10" s="14">
+        <v>50</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>30</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/12620764.xlsx
+++ b/12620764.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mishty sharma\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B79F4F-68D9-4D29-9B12-5FB06BED2957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1676BF6B-A407-43EF-A621-1F61F921D580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -240,6 +240,126 @@
   <si>
     <t>neutral</t>
   </si>
+  <si>
+    <t xml:space="preserve">homework of python </t>
+  </si>
+  <si>
+    <t>went for shopping</t>
+  </si>
+  <si>
+    <t>diagnostictest</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>jupyter download</t>
+  </si>
+  <si>
+    <t>tired and sleepy</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>sql homework to be done</t>
+  </si>
+  <si>
+    <t>missiing old friends</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>anxious</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>fever</t>
+  </si>
+  <si>
+    <t>suffering from viral</t>
+  </si>
+  <si>
+    <t>sandbox  homework</t>
+  </si>
+  <si>
+    <t>c++ doubts</t>
+  </si>
+  <si>
+    <t>analytical problem solving</t>
+  </si>
+  <si>
+    <t>feeling good, ca's alotted</t>
+  </si>
+  <si>
+    <t>communication ca</t>
+  </si>
+  <si>
+    <t>ca preperation , went out with friends</t>
+  </si>
+  <si>
+    <t>no class , took rest whole day</t>
+  </si>
+  <si>
+    <t>database ca alotted</t>
+  </si>
+  <si>
+    <t>networking ca alotted, pratice done</t>
+  </si>
+  <si>
+    <t>went for a movie</t>
+  </si>
+  <si>
+    <t>revised ca syllabus</t>
+  </si>
+  <si>
+    <t>networking,database ca done</t>
+  </si>
+  <si>
+    <t>classes got cancelled</t>
+  </si>
+  <si>
+    <t>took tuitonn classes for 3 hours</t>
+  </si>
+  <si>
+    <t>loviraj sir was on leave</t>
+  </si>
+  <si>
+    <t>minor project was allotted</t>
+  </si>
+  <si>
+    <t>practice on jupyter and having insomia</t>
+  </si>
+  <si>
+    <t>demo test of  analytical skills</t>
+  </si>
+  <si>
+    <t>ca of analytical skills was done</t>
+  </si>
+  <si>
+    <t>took rest as it was Sunday</t>
+  </si>
+  <si>
+    <t>went to uni mall with friends</t>
+  </si>
+  <si>
+    <t>started minor project of cap776</t>
+  </si>
+  <si>
+    <t>completed excel sheet of cap776</t>
+  </si>
+  <si>
+    <t>hitbulls practice test alloted</t>
+  </si>
+  <si>
+    <t>enjoyed Sunday with family</t>
+  </si>
+  <si>
+    <t>no classes till 10 oct</t>
+  </si>
 </sst>
 </file>
 
@@ -377,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -421,6 +541,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -889,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N395"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="65.21875" customWidth="1"/>
@@ -1087,11 +1210,11 @@
         <v>20</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" ref="I7:I69" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>850</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" ref="J7:J69" si="1">IF(I7="","",1440-I7)</f>
+        <f t="shared" ref="J7:J63" si="0">IF(I7="","",1440-I7)</f>
         <v>590</v>
       </c>
       <c r="K7" s="16" t="s">
@@ -1133,11 +1256,11 @@
         <v>20</v>
       </c>
       <c r="I8" s="15">
+        <f t="shared" ref="I8:I63" si="1">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
+        <v>1100</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="0"/>
-        <v>1100</v>
-      </c>
-      <c r="J8" s="15">
-        <f t="shared" si="1"/>
         <v>340</v>
       </c>
       <c r="K8" s="16" t="s">
@@ -1179,11 +1302,11 @@
         <v>20</v>
       </c>
       <c r="I9" s="15">
+        <f t="shared" si="1"/>
+        <v>960</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
-      </c>
-      <c r="J9" s="15">
-        <f t="shared" si="1"/>
         <v>480</v>
       </c>
       <c r="K9" s="16" t="s">
@@ -1225,11 +1348,11 @@
         <v>30</v>
       </c>
       <c r="I10" s="15">
+        <f t="shared" si="1"/>
+        <v>910</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>910</v>
-      </c>
-      <c r="J10" s="15">
-        <f t="shared" si="1"/>
         <v>530</v>
       </c>
       <c r="K10" s="16" t="s">
@@ -1246,821 +1369,1709 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>22</v>
+      </c>
+      <c r="D11" s="14">
+        <v>100</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>10</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="1"/>
+        <v>672</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>768</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B12" s="14">
+        <v>300</v>
+      </c>
+      <c r="C12" s="14">
+        <v>10</v>
+      </c>
+      <c r="D12" s="14">
+        <v>90</v>
+      </c>
+      <c r="E12" s="14">
+        <v>70</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>20</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B13" s="14">
+        <v>200</v>
+      </c>
+      <c r="C13" s="14">
+        <v>15</v>
+      </c>
+      <c r="D13" s="14">
+        <v>60</v>
+      </c>
+      <c r="E13" s="14">
+        <v>90</v>
+      </c>
+      <c r="F13" s="14">
+        <v>150</v>
+      </c>
+      <c r="G13" s="14">
+        <v>3</v>
+      </c>
+      <c r="H13" s="14">
+        <v>36</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+        <v>551</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>889</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B14" s="14">
+        <v>400</v>
+      </c>
+      <c r="C14" s="14">
+        <v>25</v>
+      </c>
+      <c r="D14" s="14">
+        <v>55</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>300</v>
+      </c>
+      <c r="G14" s="14">
+        <v>6</v>
+      </c>
+      <c r="H14" s="14">
+        <v>10</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="14">
+        <v>360</v>
+      </c>
+      <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>30</v>
+      </c>
+      <c r="E15" s="14">
+        <v>90</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>20</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="14">
+        <v>400</v>
+      </c>
+      <c r="C16" s="14">
+        <v>10</v>
+      </c>
+      <c r="D16" s="14">
+        <v>40</v>
+      </c>
+      <c r="E16" s="14">
+        <v>90</v>
+      </c>
+      <c r="F16" s="14">
+        <v>250</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>17</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+        <v>807</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>633</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="14">
+        <v>500</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>40</v>
+      </c>
+      <c r="E17" s="14">
+        <v>70</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>10</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>500</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="14">
+        <v>600</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>35</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>20</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+        <v>745</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>695</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B19" s="14">
+        <v>650</v>
+      </c>
+      <c r="C19" s="14">
+        <v>22</v>
+      </c>
+      <c r="D19" s="14">
+        <v>60</v>
+      </c>
+      <c r="E19" s="14">
+        <v>45</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>30</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+        <v>807</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>633</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="14">
+        <v>360</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>40</v>
+      </c>
+      <c r="E20" s="14">
+        <v>80</v>
+      </c>
+      <c r="F20" s="14">
+        <v>200</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>25</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+        <v>735</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>705</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="14">
+        <v>300</v>
+      </c>
+      <c r="C21" s="14">
+        <v>22</v>
+      </c>
+      <c r="D21" s="14">
+        <v>40</v>
+      </c>
+      <c r="E21" s="14">
+        <v>90</v>
+      </c>
+      <c r="F21" s="14">
+        <v>150</v>
+      </c>
+      <c r="G21" s="14">
+        <v>3</v>
+      </c>
+      <c r="H21" s="14">
+        <v>10</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+        <v>612</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>828</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="14">
+        <v>250</v>
+      </c>
+      <c r="C22" s="14">
+        <v>45</v>
+      </c>
+      <c r="D22" s="14">
+        <v>30</v>
+      </c>
+      <c r="E22" s="14">
+        <v>70</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>12</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+        <v>657</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>783</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="14">
+        <v>200</v>
+      </c>
+      <c r="C23" s="14">
+        <v>25</v>
+      </c>
+      <c r="D23" s="14">
+        <v>30</v>
+      </c>
+      <c r="E23" s="14">
+        <v>65</v>
+      </c>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>22</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+        <v>692</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>748</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="14">
+        <v>300</v>
+      </c>
+      <c r="C24" s="14">
+        <v>35</v>
+      </c>
+      <c r="D24" s="14">
+        <v>50</v>
+      </c>
+      <c r="E24" s="14">
+        <v>70</v>
+      </c>
+      <c r="F24" s="14">
+        <v>400</v>
+      </c>
+      <c r="G24" s="14">
+        <v>8</v>
+      </c>
+      <c r="H24" s="14">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>585</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="14">
+        <v>600</v>
+      </c>
+      <c r="C25" s="14">
+        <v>55</v>
+      </c>
+      <c r="D25" s="14">
+        <v>40</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>40</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>675</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="14">
+        <v>600</v>
+      </c>
+      <c r="C26" s="14">
+        <v>60</v>
+      </c>
+      <c r="D26" s="14">
+        <v>30</v>
+      </c>
+      <c r="E26" s="14">
+        <v>85</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>32</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+        <v>807</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>633</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="14">
+        <v>500</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>20</v>
+      </c>
+      <c r="E27" s="14">
+        <v>90</v>
+      </c>
+      <c r="F27" s="14">
+        <v>200</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>20</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="14">
+        <v>360</v>
+      </c>
+      <c r="C28" s="14">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>150</v>
+      </c>
+      <c r="E28" s="14">
+        <v>10</v>
+      </c>
+      <c r="F28" s="14">
+        <v>150</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>20</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+        <v>710</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="14">
+        <v>400</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>350</v>
+      </c>
+      <c r="E29" s="14">
+        <v>40</v>
+      </c>
+      <c r="F29" s="14">
+        <v>350</v>
+      </c>
+      <c r="G29" s="14">
+        <v>7</v>
+      </c>
+      <c r="H29" s="14">
+        <v>10</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>260</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="14">
+        <v>540</v>
+      </c>
+      <c r="C30" s="14">
+        <v>40</v>
+      </c>
+      <c r="D30" s="14">
+        <v>200</v>
+      </c>
+      <c r="E30" s="14">
+        <v>20</v>
+      </c>
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>15</v>
+      </c>
+      <c r="I30" s="15">
+        <f t="shared" ref="I30:I33" si="2">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <v>1015</v>
+      </c>
+      <c r="J30" s="15">
+        <f t="shared" si="0"/>
+        <v>425</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="14">
+        <v>500</v>
+      </c>
+      <c r="C31" s="14">
+        <v>10</v>
+      </c>
+      <c r="D31" s="14">
+        <v>0</v>
+      </c>
+      <c r="E31" s="14">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>25</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" si="2"/>
+        <v>535</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" si="0"/>
+        <v>905</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="14">
+        <v>600</v>
+      </c>
+      <c r="C32" s="14">
+        <v>25</v>
+      </c>
+      <c r="D32" s="14">
+        <v>300</v>
+      </c>
+      <c r="E32" s="14">
+        <v>25</v>
+      </c>
+      <c r="F32" s="14">
+        <v>300</v>
+      </c>
+      <c r="G32" s="14">
+        <v>6</v>
+      </c>
+      <c r="H32" s="14">
+        <v>40</v>
+      </c>
+      <c r="I32" s="15">
+        <f t="shared" si="2"/>
+        <v>1290</v>
+      </c>
+      <c r="J32" s="15">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="14">
+        <v>400</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>250</v>
+      </c>
+      <c r="E33" s="14">
+        <v>20</v>
+      </c>
+      <c r="F33" s="14">
+        <v>150</v>
+      </c>
+      <c r="G33" s="14">
+        <v>3</v>
+      </c>
+      <c r="H33" s="14">
+        <v>30</v>
+      </c>
+      <c r="I33" s="15">
+        <f t="shared" si="2"/>
+        <v>880</v>
+      </c>
+      <c r="J33" s="15">
+        <f t="shared" si="0"/>
+        <v>560</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>40</v>
+      </c>
+      <c r="D34" s="14">
+        <v>180</v>
+      </c>
+      <c r="E34" s="14">
+        <v>20</v>
+      </c>
+      <c r="F34" s="14">
+        <v>150</v>
+      </c>
+      <c r="G34" s="14">
+        <v>3</v>
+      </c>
+      <c r="H34" s="14">
+        <v>70</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>560</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B35" s="14">
+        <v>600</v>
+      </c>
+      <c r="C35" s="14">
+        <v>40</v>
+      </c>
+      <c r="D35" s="14">
+        <v>200</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>80</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>110</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="14">
+        <v>650</v>
+      </c>
+      <c r="C36" s="14">
+        <v>60</v>
+      </c>
+      <c r="D36" s="14">
+        <v>200</v>
+      </c>
+      <c r="E36" s="14">
+        <v>30</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>70</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>230</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B37" s="14">
+        <v>600</v>
+      </c>
+      <c r="C37" s="14">
+        <v>45</v>
+      </c>
+      <c r="D37" s="14">
+        <v>100</v>
+      </c>
+      <c r="E37" s="14">
+        <v>45</v>
+      </c>
+      <c r="F37" s="14">
+        <v>300</v>
+      </c>
+      <c r="G37" s="14">
+        <v>6</v>
+      </c>
+      <c r="H37" s="14">
+        <v>50</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>300</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="14">
+        <v>400</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>200</v>
+      </c>
+      <c r="E38" s="14">
+        <v>30</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>80</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>450</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="14">
+        <v>500</v>
+      </c>
+      <c r="C39" s="14">
+        <v>40</v>
+      </c>
+      <c r="D39" s="14">
+        <v>250</v>
+      </c>
+      <c r="E39" s="14">
+        <v>50</v>
+      </c>
+      <c r="F39" s="14">
+        <v>150</v>
+      </c>
+      <c r="G39" s="14">
+        <v>3</v>
+      </c>
+      <c r="H39" s="14">
+        <v>90</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>360</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="14">
+        <v>800</v>
+      </c>
+      <c r="C40" s="14">
+        <v>20</v>
+      </c>
+      <c r="D40" s="14">
+        <v>100</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>30</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="14">
+        <v>400</v>
+      </c>
+      <c r="C41" s="14">
+        <v>30</v>
+      </c>
+      <c r="D41" s="14">
+        <v>400</v>
+      </c>
+      <c r="E41" s="14">
+        <v>70</v>
+      </c>
+      <c r="F41" s="14">
+        <v>150</v>
+      </c>
+      <c r="G41" s="14">
+        <v>3</v>
+      </c>
+      <c r="H41" s="14">
+        <v>70</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>320</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="14">
+        <v>500</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>200</v>
+      </c>
+      <c r="E42" s="14">
+        <v>45</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>50</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>265</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="14">
+        <v>600</v>
+      </c>
+      <c r="C43" s="14">
+        <v>40</v>
+      </c>
+      <c r="D43" s="14">
+        <v>300</v>
+      </c>
+      <c r="E43" s="14">
+        <v>60</v>
+      </c>
+      <c r="F43" s="14">
+        <v>200</v>
+      </c>
+      <c r="G43" s="14">
+        <v>4</v>
+      </c>
+      <c r="H43" s="14">
+        <v>35</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+        <v>1235</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>205</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="14">
+        <v>650</v>
+      </c>
+      <c r="C44" s="21">
+        <v>45</v>
+      </c>
+      <c r="D44" s="14">
+        <v>150</v>
+      </c>
+      <c r="E44" s="14">
+        <v>70</v>
+      </c>
+      <c r="F44" s="14">
+        <v>350</v>
+      </c>
+      <c r="G44" s="14">
+        <v>7</v>
+      </c>
+      <c r="H44" s="14">
+        <v>40</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+        <v>1305</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>135</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B45" s="14">
+        <v>700</v>
+      </c>
+      <c r="C45" s="14">
+        <v>40</v>
+      </c>
+      <c r="D45" s="14">
+        <v>100</v>
+      </c>
+      <c r="E45" s="14">
+        <v>50</v>
+      </c>
+      <c r="F45" s="14">
+        <v>300</v>
+      </c>
+      <c r="G45" s="14">
+        <v>6</v>
+      </c>
+      <c r="H45" s="14">
+        <v>50</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>200</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B46" s="14">
+        <v>600</v>
+      </c>
+      <c r="C46" s="14">
+        <v>50</v>
+      </c>
+      <c r="D46" s="14">
+        <v>200</v>
+      </c>
+      <c r="E46" s="14">
+        <v>60</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>80</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>450</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B47" s="14">
+        <v>500</v>
+      </c>
+      <c r="C47" s="14">
+        <v>45</v>
+      </c>
+      <c r="D47" s="14">
+        <v>100</v>
+      </c>
+      <c r="E47" s="14">
+        <v>35</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>75</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+        <v>755</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+        <v>685</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>71</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
+      <c r="A48" s="13">
+        <v>46293</v>
+      </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -2069,11 +3080,11 @@
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
       <c r="I48" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J48" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K48" s="16"/>
@@ -2082,7 +3093,9 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
+      <c r="A49" s="13">
+        <v>46294</v>
+      </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -2091,11 +3104,11 @@
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J49" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K49" s="16"/>
@@ -2104,7 +3117,9 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
+      <c r="A50" s="13">
+        <v>46295</v>
+      </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -2113,11 +3128,11 @@
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
       <c r="I50" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J50" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K50" s="16"/>
@@ -2126,7 +3141,9 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
+      <c r="A51" s="13">
+        <v>46296</v>
+      </c>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -2135,11 +3152,11 @@
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
       <c r="I51" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J51" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K51" s="16"/>
@@ -2148,7 +3165,9 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
+      <c r="A52" s="13">
+        <v>46297</v>
+      </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -2157,11 +3176,11 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
       <c r="I52" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J52" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K52" s="16"/>
@@ -2170,7 +3189,9 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
+      <c r="A53" s="13">
+        <v>46298</v>
+      </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -2179,11 +3200,11 @@
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J53" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K53" s="16"/>
@@ -2192,7 +3213,9 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
+      <c r="A54" s="13">
+        <v>46299</v>
+      </c>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
@@ -2201,11 +3224,11 @@
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
       <c r="I54" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J54" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K54" s="16"/>
@@ -2214,7 +3237,9 @@
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
+      <c r="A55" s="13">
+        <v>46300</v>
+      </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -2223,11 +3248,11 @@
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
       <c r="I55" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J55" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K55" s="16"/>
@@ -2236,7 +3261,9 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
+      <c r="A56" s="13">
+        <v>46301</v>
+      </c>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -2245,11 +3272,11 @@
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
       <c r="I56" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J56" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K56" s="16"/>
@@ -2258,7 +3285,9 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
+      <c r="A57" s="13">
+        <v>46302</v>
+      </c>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -2267,11 +3296,11 @@
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J57" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K57" s="16"/>
@@ -2280,7 +3309,9 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
+      <c r="A58" s="13">
+        <v>46303</v>
+      </c>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2289,11 +3320,11 @@
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
       <c r="I58" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J58" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K58" s="16"/>
@@ -2302,7 +3333,9 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
+      <c r="A59" s="13">
+        <v>46304</v>
+      </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -2311,11 +3344,11 @@
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
       <c r="I59" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J59" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K59" s="16"/>
@@ -2324,7 +3357,9 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
+      <c r="A60" s="13">
+        <v>46305</v>
+      </c>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
@@ -2333,11 +3368,11 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J60" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K60" s="16"/>
@@ -2346,7 +3381,9 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
+      <c r="A61" s="13">
+        <v>46306</v>
+      </c>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
@@ -2355,11 +3392,11 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J61" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K61" s="16"/>
@@ -2368,7 +3405,9 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
+      <c r="A62" s="13">
+        <v>46307</v>
+      </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -2377,11 +3416,11 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J62" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K62" s="16"/>
@@ -2390,7 +3429,9 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
+      <c r="A63" s="13">
+        <v>46308</v>
+      </c>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -2399,11 +3440,11 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J63" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K63" s="16"/>
@@ -2412,7 +3453,9 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
+      <c r="A64" s="13">
+        <v>46309</v>
+      </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -2421,11 +3464,11 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I64:I127" si="3">IF(SUM(B64:F64,H64)=0,"",SUM(B64:F64,H64))</f>
         <v/>
       </c>
       <c r="J64" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J64:J127" si="4">IF(I64="","",1440-I64)</f>
         <v/>
       </c>
       <c r="K64" s="16"/>
@@ -2434,7 +3477,9 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
+      <c r="A65" s="13">
+        <v>46310</v>
+      </c>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -2443,11 +3488,11 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K65" s="16"/>
@@ -2456,7 +3501,9 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
+      <c r="A66" s="13">
+        <v>46311</v>
+      </c>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -2465,11 +3512,11 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J66" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K66" s="16"/>
@@ -2478,7 +3525,9 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
+      <c r="A67" s="13">
+        <v>46312</v>
+      </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -2487,11 +3536,11 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J67" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K67" s="16"/>
@@ -2500,7 +3549,9 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
+      <c r="A68" s="13">
+        <v>46313</v>
+      </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -2509,11 +3560,11 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -2522,7 +3573,9 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
+      <c r="A69" s="13">
+        <v>46314</v>
+      </c>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -2531,11 +3584,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -2544,7 +3597,9 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
+      <c r="A70" s="13">
+        <v>46315</v>
+      </c>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -2553,11 +3608,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2566,7 +3621,9 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
+      <c r="A71" s="13">
+        <v>46316</v>
+      </c>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -2575,11 +3632,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2588,7 +3645,9 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
+      <c r="A72" s="13">
+        <v>46317</v>
+      </c>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -2597,11 +3656,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2610,7 +3669,9 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
+      <c r="A73" s="13">
+        <v>46318</v>
+      </c>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -2619,11 +3680,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2632,7 +3693,9 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
+      <c r="A74" s="13">
+        <v>46319</v>
+      </c>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -2641,11 +3704,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2654,7 +3717,9 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
+      <c r="A75" s="13">
+        <v>46320</v>
+      </c>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -2663,11 +3728,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2676,7 +3741,9 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
+      <c r="A76" s="13">
+        <v>46321</v>
+      </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -2685,11 +3752,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2698,7 +3765,9 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
+      <c r="A77" s="13">
+        <v>46322</v>
+      </c>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -2707,11 +3776,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2720,7 +3789,9 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
+      <c r="A78" s="13">
+        <v>46323</v>
+      </c>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -2729,11 +3800,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2751,11 +3822,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2773,11 +3844,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2795,11 +3866,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2817,11 +3888,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2839,11 +3910,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2861,11 +3932,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -2883,11 +3954,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -2905,11 +3976,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -2927,11 +3998,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -2949,11 +4020,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -2971,11 +4042,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -2993,11 +4064,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3015,11 +4086,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3037,11 +4108,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3059,11 +4130,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3081,11 +4152,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3103,11 +4174,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3125,11 +4196,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3147,11 +4218,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3169,11 +4240,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3191,11 +4262,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3213,11 +4284,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3235,11 +4306,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3257,11 +4328,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3279,11 +4350,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3301,11 +4372,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3323,11 +4394,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3345,11 +4416,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3367,11 +4438,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3389,11 +4460,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3411,11 +4482,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3433,11 +4504,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3455,11 +4526,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3477,11 +4548,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3499,11 +4570,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3521,11 +4592,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3543,11 +4614,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3565,11 +4636,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3587,11 +4658,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3609,11 +4680,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3631,11 +4702,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3653,11 +4724,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3675,11 +4746,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3697,11 +4768,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3719,11 +4790,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3741,11 +4812,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3763,11 +4834,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3785,11 +4856,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3807,11 +4878,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3829,11 +4900,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I128:I191" si="5">IF(SUM(B128:F128,H128)=0,"",SUM(B128:F128,H128))</f>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J128:J191" si="6">IF(I128="","",1440-I128)</f>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3851,11 +4922,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -3873,11 +4944,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -3895,11 +4966,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -3917,11 +4988,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -3939,11 +5010,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -3961,11 +5032,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -3983,11 +5054,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4005,11 +5076,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4027,11 +5098,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4049,11 +5120,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4071,11 +5142,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4093,11 +5164,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4115,11 +5186,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4137,11 +5208,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4159,11 +5230,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4181,11 +5252,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4203,11 +5274,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4225,11 +5296,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4247,11 +5318,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4269,11 +5340,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4291,11 +5362,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4313,11 +5384,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4335,11 +5406,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4357,11 +5428,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4379,11 +5450,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4401,11 +5472,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4423,11 +5494,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4445,11 +5516,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4467,11 +5538,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4489,11 +5560,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4511,11 +5582,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4533,11 +5604,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4555,11 +5626,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4577,11 +5648,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4599,11 +5670,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4621,11 +5692,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4643,11 +5714,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4665,11 +5736,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4687,11 +5758,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4709,11 +5780,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4731,11 +5802,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4753,11 +5824,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4775,11 +5846,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4797,11 +5868,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4819,11 +5890,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4841,11 +5912,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4863,11 +5934,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -4885,11 +5956,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -4907,11 +5978,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -4929,11 +6000,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -4951,11 +6022,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -4973,11 +6044,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -4995,11 +6066,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5017,11 +6088,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5039,11 +6110,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5061,11 +6132,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5083,11 +6154,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5105,11 +6176,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5127,11 +6198,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5149,11 +6220,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5171,11 +6242,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5193,11 +6264,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5215,11 +6286,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5237,11 +6308,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I192:I255" si="7">IF(SUM(B192:F192,H192)=0,"",SUM(B192:F192,H192))</f>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J192:J255" si="8">IF(I192="","",1440-I192)</f>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5259,11 +6330,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5281,11 +6352,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5303,11 +6374,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5325,11 +6396,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5347,11 +6418,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5369,11 +6440,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5391,11 +6462,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5413,11 +6484,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5435,11 +6506,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5457,11 +6528,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5479,11 +6550,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5501,11 +6572,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5523,11 +6594,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5545,11 +6616,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5567,11 +6638,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5589,11 +6660,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5611,11 +6682,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5633,11 +6704,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5655,11 +6726,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5677,11 +6748,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5699,11 +6770,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5721,11 +6792,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5743,11 +6814,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5765,11 +6836,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5787,11 +6858,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5809,11 +6880,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5831,11 +6902,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5853,11 +6924,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -5875,11 +6946,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -5897,11 +6968,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -5919,11 +6990,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -5941,11 +7012,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -5963,11 +7034,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -5985,11 +7056,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6007,11 +7078,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6029,11 +7100,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6051,11 +7122,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6073,11 +7144,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6095,11 +7166,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6117,11 +7188,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6139,11 +7210,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6161,11 +7232,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6183,11 +7254,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6205,11 +7276,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6227,11 +7298,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6249,11 +7320,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6271,11 +7342,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6293,11 +7364,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6315,11 +7386,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6337,11 +7408,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6359,11 +7430,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6381,11 +7452,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6403,11 +7474,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6425,11 +7496,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6447,11 +7518,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6469,11 +7540,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6491,11 +7562,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6513,11 +7584,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6535,11 +7606,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6557,11 +7628,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6579,11 +7650,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6601,11 +7672,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6623,11 +7694,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6645,11 +7716,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I256:I319" si="9">IF(SUM(B256:F256,H256)=0,"",SUM(B256:F256,H256))</f>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J256:J319" si="10">IF(I256="","",1440-I256)</f>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6667,11 +7738,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6689,11 +7760,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6711,11 +7782,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6733,11 +7804,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6755,11 +7826,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6777,11 +7848,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6799,11 +7870,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6821,11 +7892,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6843,11 +7914,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6865,11 +7936,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -6887,11 +7958,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -6909,11 +7980,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -6931,11 +8002,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -6953,11 +8024,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -6975,11 +8046,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -6997,11 +8068,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7019,11 +8090,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7041,11 +8112,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7063,11 +8134,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7085,11 +8156,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7107,11 +8178,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7129,11 +8200,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7151,11 +8222,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7173,11 +8244,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7195,11 +8266,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7217,11 +8288,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7239,11 +8310,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7261,11 +8332,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7283,11 +8354,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7305,11 +8376,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7327,11 +8398,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7349,11 +8420,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7371,11 +8442,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7393,11 +8464,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7415,11 +8486,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7437,11 +8508,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7459,11 +8530,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7481,11 +8552,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7503,11 +8574,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7525,11 +8596,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7547,11 +8618,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7569,11 +8640,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7591,11 +8662,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7613,11 +8684,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7635,11 +8706,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7657,11 +8728,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7679,11 +8750,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7701,11 +8772,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7723,11 +8794,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7745,11 +8816,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7767,11 +8838,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7789,11 +8860,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7811,11 +8882,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7833,11 +8904,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7855,11 +8926,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -7877,11 +8948,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -7899,11 +8970,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -7921,11 +8992,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -7943,11 +9014,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -7965,11 +9036,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -7987,11 +9058,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8009,11 +9080,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8031,11 +9102,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8053,11 +9124,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I320:I383" si="11">IF(SUM(B320:F320,H320)=0,"",SUM(B320:F320,H320))</f>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J320:J383" si="12">IF(I320="","",1440-I320)</f>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8075,11 +9146,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8097,11 +9168,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8119,11 +9190,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8141,11 +9212,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8163,11 +9234,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8185,11 +9256,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8207,11 +9278,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8229,11 +9300,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8251,11 +9322,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8273,11 +9344,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8295,11 +9366,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8317,11 +9388,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8339,11 +9410,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8361,11 +9432,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8383,11 +9454,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8405,11 +9476,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8427,11 +9498,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8449,11 +9520,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8471,11 +9542,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8493,11 +9564,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8515,11 +9586,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8537,11 +9608,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8559,11 +9630,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8581,11 +9652,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8603,11 +9674,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8625,11 +9696,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8647,11 +9718,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8669,11 +9740,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8691,11 +9762,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8713,11 +9784,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8735,11 +9806,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8757,11 +9828,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8779,11 +9850,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8801,11 +9872,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8823,11 +9894,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8845,11 +9916,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -8867,11 +9938,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -8889,11 +9960,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -8911,11 +9982,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -8933,11 +10004,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -8955,11 +10026,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -8977,11 +10048,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -8999,11 +10070,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9021,11 +10092,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9043,11 +10114,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9065,11 +10136,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9087,11 +10158,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9109,11 +10180,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9131,11 +10202,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9153,11 +10224,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9175,11 +10246,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9197,11 +10268,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9219,11 +10290,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9241,11 +10312,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9263,11 +10334,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9285,11 +10356,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9307,11 +10378,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9329,11 +10400,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9351,11 +10422,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9373,11 +10444,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9395,11 +10466,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9417,11 +10488,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9439,11 +10510,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9461,11 +10532,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I384:I395" si="13">IF(SUM(B384:F384,H384)=0,"",SUM(B384:F384,H384))</f>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J384:J395" si="14">IF(I384="","",1440-I384)</f>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9483,11 +10554,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9505,11 +10576,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9527,11 +10598,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9549,11 +10620,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9571,11 +10642,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9593,11 +10664,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9615,11 +10686,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9637,11 +10708,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9659,11 +10730,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9681,11 +10752,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9703,149 +10774,17 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
       <c r="L395" s="16"/>
       <c r="M395" s="16"/>
       <c r="N395" s="17"/>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A396" s="13"/>
-      <c r="B396" s="14"/>
-      <c r="C396" s="14"/>
-      <c r="D396" s="14"/>
-      <c r="E396" s="14"/>
-      <c r="F396" s="14"/>
-      <c r="G396" s="14"/>
-      <c r="H396" s="14"/>
-      <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K396" s="16"/>
-      <c r="L396" s="16"/>
-      <c r="M396" s="16"/>
-      <c r="N396" s="17"/>
-    </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A397" s="13"/>
-      <c r="B397" s="14"/>
-      <c r="C397" s="14"/>
-      <c r="D397" s="14"/>
-      <c r="E397" s="14"/>
-      <c r="F397" s="14"/>
-      <c r="G397" s="14"/>
-      <c r="H397" s="14"/>
-      <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K397" s="16"/>
-      <c r="L397" s="16"/>
-      <c r="M397" s="16"/>
-      <c r="N397" s="17"/>
-    </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A398" s="13"/>
-      <c r="B398" s="14"/>
-      <c r="C398" s="14"/>
-      <c r="D398" s="14"/>
-      <c r="E398" s="14"/>
-      <c r="F398" s="14"/>
-      <c r="G398" s="14"/>
-      <c r="H398" s="14"/>
-      <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K398" s="16"/>
-      <c r="L398" s="16"/>
-      <c r="M398" s="16"/>
-      <c r="N398" s="17"/>
-    </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A399" s="13"/>
-      <c r="B399" s="14"/>
-      <c r="C399" s="14"/>
-      <c r="D399" s="14"/>
-      <c r="E399" s="14"/>
-      <c r="F399" s="14"/>
-      <c r="G399" s="14"/>
-      <c r="H399" s="14"/>
-      <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K399" s="16"/>
-      <c r="L399" s="16"/>
-      <c r="M399" s="16"/>
-      <c r="N399" s="17"/>
-    </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A400" s="13"/>
-      <c r="B400" s="14"/>
-      <c r="C400" s="14"/>
-      <c r="D400" s="14"/>
-      <c r="E400" s="14"/>
-      <c r="F400" s="14"/>
-      <c r="G400" s="14"/>
-      <c r="H400" s="14"/>
-      <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K400" s="16"/>
-      <c r="L400" s="16"/>
-      <c r="M400" s="16"/>
-      <c r="N400" s="17"/>
-    </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -9856,26 +10795,26 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J395">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K395" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L395" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M395" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12620764.xlsx
+++ b/12620764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mishty sharma\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1676BF6B-A407-43EF-A621-1F61F921D580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E028484-4996-43E4-B274-0467B6D5D68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>no classes till 10 oct</t>
+  </si>
+  <si>
+    <t>worried as my friend is stuck in hostel</t>
   </si>
 </sst>
 </file>
@@ -3024,7 +3027,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="13">
         <v>46292</v>
       </c>
@@ -3066,7 +3069,9 @@
       <c r="M47" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="N47" s="17"/>
+      <c r="N47" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13">
